--- a/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E165FF5-B7E2-4D4F-8833-5744BD4178A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD6F655-EB68-4A59-9035-EDA94EA2A349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8590" uniqueCount="1967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8580" uniqueCount="1964">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -6018,15 +6018,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_IT10-380,e_IT156-380,e_IT157-380,e_IT158-380,e_IT159-380,e_IT21-380,e_IT42-380,e_IT7-380,e_IT8-380,e_IT9-380,e_IT90-400,e_IT93-380,e_w100113593-380,e_w100407576-380,e_w103381531-380,e_w103653592-380,e_w105757794-380,e_w109588422-380,e_w109756016-380,e_w109993642-380,e_w109997676-380,e_w110138220-380,e_w1103579629-380,e_w110660048-380,e_w1117128898-380,e_w114661587-380,e_w1158716725,e_w118987056-380,e_w143585004-380,e_w145665799-380,e_w145665862-380,e_w146791215-380,e_w149997403-380,e_w155590373-380,e_w157912118-380,e_w158739183-380,e_w172302572-380,e_w199675964-380,e_w203225567,e_w255011550-380,e_w303915533-380,e_w338753171-380,e_w36873258-380,e_w409439916-380,e_w411026199-380,e_w414663585-380,e_w416989699-380,e_w418902800-380,e_w432729521-380,e_w491424937-380,e_w491424937-400,e_w58992998-380,e_w591027058-380,e_w59219335-380,e_w59462715-380,e_w60725875-380,e_w60913666-380,e_w60919237-380,e_w72570378-380,e_w72570474-380,e_w743450089-380,e_w74943205-380,e_w81929591-380,e_w82759380-380,e_w82762493-380,e_w82767145-380,e_w83872215-380</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -7241,10 +7232,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD987748-81EF-4E3D-A663-FA4EE2C832B1}">
-  <dimension ref="B2:AJ1102"/>
+  <dimension ref="B2:AF1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -7257,11 +7248,8 @@
       <c r="U2" t="s">
         <v>701</v>
       </c>
-      <c r="AH2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -7313,17 +7301,8 @@
       <c r="AA3" t="s">
         <v>451</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>452</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>135</v>
       </c>
@@ -7390,17 +7369,8 @@
       <c r="AF4" t="s">
         <v>1961</v>
       </c>
-      <c r="AH4" t="s">
-        <v>1964</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>1965</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>136</v>
       </c>
@@ -7464,17 +7434,8 @@
       <c r="AF5" t="s">
         <v>1962</v>
       </c>
-      <c r="AH5" t="s">
-        <v>1966</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>1965</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>137</v>
       </c>
@@ -7539,7 +7500,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>138</v>
       </c>
@@ -7589,7 +7550,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>139</v>
       </c>
@@ -7639,7 +7600,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>140</v>
       </c>
@@ -7689,7 +7650,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>141</v>
       </c>
@@ -7739,7 +7700,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>142</v>
       </c>
@@ -7789,7 +7750,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>143</v>
       </c>
@@ -7839,7 +7800,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>144</v>
       </c>
@@ -7889,7 +7850,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>145</v>
       </c>
@@ -7939,7 +7900,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>146</v>
       </c>
@@ -7989,7 +7950,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>147</v>
       </c>

--- a/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD6F655-EB68-4A59-9035-EDA94EA2A349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8D609BA-47FE-4603-A5A2-FF254BE37DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -7231,7 +7231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD987748-81EF-4E3D-A663-FA4EE2C832B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AFF6EEA-E274-4A2B-A919-DBAA70A6408B}">
   <dimension ref="B2:AF1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32390,7 +32390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BEEDD6-7CDF-4C37-B45C-4092C6F69B1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE94ABAC-7FDB-45D0-B4AB-4B603E845192}">
   <dimension ref="B9:L43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A99A8BFE-4F00-4DC3-AC74-F8D32757B539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCEF4AB1-0443-4CA6-B31D-DA3DA33D6DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6512,7 +6512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AAA621-0805-4E7C-8D36-086FEA54CEA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88116CFF-6DF5-430A-8BB4-E8B246384AC3}">
   <dimension ref="B2:AF1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31671,7 +31671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B316AE06-F29E-4B13-B44D-7F9A18C20485}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A964A265-83FD-419D-AA01-3C566479ED81}">
   <dimension ref="B9:L43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
